--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82E09F8-7021-42C3-B4C7-C293B6C8AE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0600709F-3C4F-4A13-8A24-390AA57E06C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-2820" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,15 +26,173 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Mikael Løvig Larsen</author>
+  </authors>
+  <commentList>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{83D0CFFF-C029-459E-9523-597C936FA63D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Mikael Løvig Larsen:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+no container mass</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>triplicate measurements on same sample at different locations</t>
+  </si>
+  <si>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>AA</t>
+  </si>
+  <si>
+    <t>H2SO4</t>
+  </si>
+  <si>
+    <t>Untreated</t>
+  </si>
+  <si>
+    <t>V acid [mL]</t>
+  </si>
+  <si>
+    <t>pH before</t>
+  </si>
+  <si>
+    <t>500 g slurry acidified for each treatment</t>
+  </si>
+  <si>
+    <t>pH after</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>pH before exp</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>untreated1</t>
+  </si>
+  <si>
+    <t>untreated2</t>
+  </si>
+  <si>
+    <t>untreated3</t>
+  </si>
+  <si>
+    <t>AA1</t>
+  </si>
+  <si>
+    <t>AA2</t>
+  </si>
+  <si>
+    <t>AA3</t>
+  </si>
+  <si>
+    <t>H2SO4 1</t>
+  </si>
+  <si>
+    <t>H2SO4 2</t>
+  </si>
+  <si>
+    <t>H2SO4 3</t>
+  </si>
+  <si>
+    <t>STD 1</t>
+  </si>
+  <si>
+    <t>STD 2</t>
+  </si>
+  <si>
+    <t>m(slurry) [g]</t>
+  </si>
+  <si>
+    <t>49 mL of water for slurry samples</t>
+  </si>
+  <si>
+    <t>24.5 for stds</t>
+  </si>
+  <si>
+    <t>NH4 measurement [mg/L]</t>
+  </si>
+  <si>
+    <t>41*</t>
+  </si>
+  <si>
+    <t>Crucible nr</t>
+  </si>
+  <si>
+    <t>m(sample, wet) [g]</t>
+  </si>
+  <si>
+    <t>m(container) [g]</t>
+  </si>
+  <si>
+    <t>Untr</t>
+  </si>
+  <si>
+    <t>Decription</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -57,8 +215,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -339,27 +500,430 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="56.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="E2">
+        <v>7.06</v>
+      </c>
+      <c r="F2">
+        <v>6.22</v>
+      </c>
+      <c r="G2">
+        <v>6.39</v>
+      </c>
+      <c r="H2" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>0.79</v>
+      </c>
+      <c r="E3">
+        <v>7.09</v>
+      </c>
+      <c r="F3">
+        <v>6.23</v>
+      </c>
+      <c r="G3">
+        <v>6.43</v>
+      </c>
+      <c r="H3">
+        <v>6.41</v>
+      </c>
+      <c r="I3">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>6.95</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>7.04</v>
+      </c>
+      <c r="H4">
+        <v>7.04</v>
+      </c>
+      <c r="I4">
+        <v>7.04</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F7390D-8C65-402E-B031-C0A94901E7D3}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>1.0589</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
+        <v>1.0946</v>
+      </c>
+      <c r="E3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>1.0609999999999999</v>
+      </c>
+      <c r="E4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>1.0511999999999999</v>
+      </c>
+      <c r="E5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>1.0470999999999999</v>
+      </c>
+      <c r="E6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7">
+        <v>1.0250999999999999</v>
+      </c>
+      <c r="E7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
+        <v>1.0347999999999999</v>
+      </c>
+      <c r="E8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1.0647</v>
+      </c>
+      <c r="E9">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>1.0263</v>
+      </c>
+      <c r="E10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="E11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12">
+        <v>0.49830000000000002</v>
+      </c>
+      <c r="E12">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D6C95A-479E-4C84-94F4-777190CE73FB}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D6C95A-479E-4C84-94F4-777190CE73FB}">
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="3">
+        <v>30.201000000000001</v>
+      </c>
+      <c r="F2">
+        <v>31.996500000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>31.4588</v>
+      </c>
+      <c r="F3">
+        <v>34.002499999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>31.767600000000002</v>
+      </c>
+      <c r="F4">
+        <v>33.357100000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>32.648000000000003</v>
+      </c>
+      <c r="F5">
+        <v>34.054900000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6">
+        <v>30.0655</v>
+      </c>
+      <c r="F6">
+        <v>33.6218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>30.7576</v>
+      </c>
+      <c r="F7">
+        <v>35.097200000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>34.088799999999999</v>
+      </c>
+      <c r="F8">
+        <v>33.154800000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <v>212</v>
+      </c>
+      <c r="D9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>37.302900000000001</v>
+      </c>
+      <c r="F9">
+        <v>31.262699999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>37.472499999999997</v>
+      </c>
+      <c r="F10">
+        <v>34.545499999999997</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0600709F-3C4F-4A13-8A24-390AA57E06C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFAFAC6-669B-4915-9A35-48C26E68B2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-2820" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
     <sheet name="TAN" sheetId="2" r:id="rId2"/>
     <sheet name="Dry-matter" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -30,6 +41,8 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Mikael Løvig Larsen</author>
+    <author>tc={DE2B62CE-1197-4D9A-AE1C-C60E9F763AD9}</author>
+    <author>tc={0B6EC8EA-5D5D-4522-94CA-748C2EF8976E}</author>
   </authors>
   <commentList>
     <comment ref="E1" authorId="0" shapeId="0" xr:uid="{83D0CFFF-C029-459E-9523-597C936FA63D}">
@@ -56,12 +69,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{DE2B62CE-1197-4D9A-AE1C-C60E9F763AD9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sample + crucible</t>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="2" shapeId="0" xr:uid="{0B6EC8EA-5D5D-4522-94CA-748C2EF8976E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Acidification homogenzes the sample?</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>Description</t>
   </si>
@@ -147,9 +176,6 @@
     <t>NH4 measurement [mg/L]</t>
   </si>
   <si>
-    <t>41*</t>
-  </si>
-  <si>
     <t>Crucible nr</t>
   </si>
   <si>
@@ -163,6 +189,30 @@
   </si>
   <si>
     <t>Decription</t>
+  </si>
+  <si>
+    <t>DF</t>
+  </si>
+  <si>
+    <t>NH4-N sample[g/L]</t>
+  </si>
+  <si>
+    <t>m after oven [g]</t>
+  </si>
+  <si>
+    <t>m dry [g]</t>
+  </si>
+  <si>
+    <t>%DM</t>
+  </si>
+  <si>
+    <t>m(ash) + crucible [g]</t>
+  </si>
+  <si>
+    <t>m(ash) [g]</t>
+  </si>
+  <si>
+    <t>%ash</t>
   </si>
 </sst>
 </file>
@@ -170,8 +220,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -218,8 +268,8 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -235,6 +285,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Mikael Løvig Larsen" id="{380A6CCD-0068-49C3-8C44-2C89BA86DCBA}" userId="S::au705323@uni.au.dk::501b5c6e-34b9-41fc-bcf2-dc0650cde639" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -498,6 +554,17 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G1" dT="2026-01-08T13:03:57.50" personId="{380A6CCD-0068-49C3-8C44-2C89BA86DCBA}" id="{DE2B62CE-1197-4D9A-AE1C-C60E9F763AD9}">
+    <text>Sample + crucible</text>
+  </threadedComment>
+  <threadedComment ref="I5" dT="2026-01-08T14:22:31.22" personId="{380A6CCD-0068-49C3-8C44-2C89BA86DCBA}" id="{0B6EC8EA-5D5D-4522-94CA-748C2EF8976E}">
+    <text>Acidification homogenzes the sample?</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I4"/>
@@ -612,16 +679,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F7390D-8C65-402E-B031-C0A94901E7D3}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -634,8 +703,14 @@
       <c r="E1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -645,11 +720,18 @@
       <c r="D2">
         <v>1.0589</v>
       </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2">
+        <v>41</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2" s="1">
+        <f>((E2*F2)/D2)/1000</f>
+        <v>1.9359712909623195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -662,8 +744,15 @@
       <c r="E3">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" ref="G3:G12" si="0">((E3*F3)/D3)/1000</f>
+        <v>2.0098666179426274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>15</v>
       </c>
@@ -673,8 +762,15 @@
       <c r="E4">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="0"/>
+        <v>1.9321394910461829</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>16</v>
       </c>
@@ -684,8 +780,15 @@
       <c r="E5">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="0"/>
+        <v>1.8550228310502284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>17</v>
       </c>
@@ -695,8 +798,15 @@
       <c r="E6">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>1.8145353834399773</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>18</v>
       </c>
@@ -706,8 +816,15 @@
       <c r="E7">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>50</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>1.9022534386889085</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>19</v>
       </c>
@@ -717,8 +834,15 @@
       <c r="E8">
         <v>39</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>1.8844221105527641</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>20</v>
       </c>
@@ -728,8 +852,15 @@
       <c r="E9">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>1.6906170752324599</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>21</v>
       </c>
@@ -739,8 +870,15 @@
       <c r="E10">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>50</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>1.900029231218942</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>22</v>
       </c>
@@ -750,8 +888,15 @@
       <c r="E11">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>6.808943089430894</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>23</v>
       </c>
@@ -760,6 +905,13 @@
       </c>
       <c r="E12">
         <v>57</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>5.7194461167971102</v>
       </c>
     </row>
   </sheetData>
@@ -769,7 +921,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D6C95A-479E-4C84-94F4-777190CE73FB}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -777,31 +929,51 @@
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C2">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" s="3">
         <v>30.201000000000001</v>
@@ -809,13 +981,35 @@
       <c r="F2">
         <v>31.996500000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2">
+        <v>34.027200000000001</v>
+      </c>
+      <c r="H2">
+        <f>G2-F2</f>
+        <v>2.0306999999999995</v>
+      </c>
+      <c r="I2" s="1">
+        <f>(H2/E2)*100</f>
+        <v>6.7239495380947627</v>
+      </c>
+      <c r="J2">
+        <v>32.394799999999996</v>
+      </c>
+      <c r="K2">
+        <f>J2-F2</f>
+        <v>0.39829999999999544</v>
+      </c>
+      <c r="L2" s="1">
+        <f>(K2/H2)*100</f>
+        <v>19.613926232333458</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3">
         <v>31.4588</v>
@@ -823,13 +1017,35 @@
       <c r="F3">
         <v>34.002499999999998</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3">
+        <v>35.564700000000002</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H10" si="0">G3-F3</f>
+        <v>1.5622000000000043</v>
+      </c>
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I10" si="1">(H3/E3)*100</f>
+        <v>4.9658601090950842</v>
+      </c>
+      <c r="J3">
+        <v>34.417700000000004</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K10" si="2">J3-F3</f>
+        <v>0.41520000000000579</v>
+      </c>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:L10" si="3">(K3/H3)*100</f>
+        <v>26.57790295736811</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>31.767600000000002</v>
@@ -837,8 +1053,30 @@
       <c r="F4">
         <v>33.357100000000003</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4">
+        <v>36.188099999999999</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>2.830999999999996</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="1"/>
+        <v>8.9115954620430742</v>
+      </c>
+      <c r="J4" s="1">
+        <v>33.775100000000002</v>
+      </c>
+      <c r="K4" s="3">
+        <f t="shared" si="2"/>
+        <v>0.41799999999999926</v>
+      </c>
+      <c r="L4" s="1">
+        <f t="shared" si="3"/>
+        <v>14.765100671140935</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>10</v>
       </c>
@@ -851,8 +1089,30 @@
       <c r="F5">
         <v>34.054900000000004</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="3">
+        <v>36.378</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>2.3230999999999966</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="1"/>
+        <v>7.1155966674834499</v>
+      </c>
+      <c r="J5">
+        <v>34.533900000000003</v>
+      </c>
+      <c r="K5" s="3">
+        <f t="shared" si="2"/>
+        <v>0.4789999999999992</v>
+      </c>
+      <c r="L5" s="1">
+        <f t="shared" si="3"/>
+        <v>20.619000473505224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>20</v>
       </c>
@@ -865,8 +1125,30 @@
       <c r="F6">
         <v>33.6218</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G6">
+        <v>35.732399999999998</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>2.110599999999998</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="1"/>
+        <v>7.0200063195356739</v>
+      </c>
+      <c r="J6">
+        <v>34.061399999999999</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="2"/>
+        <v>0.43959999999999866</v>
+      </c>
+      <c r="L6" s="1">
+        <f t="shared" si="3"/>
+        <v>20.828200511702789</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>15</v>
       </c>
@@ -879,8 +1161,30 @@
       <c r="F7">
         <v>35.097200000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7">
+        <v>37.2425</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>2.1452999999999989</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="1"/>
+        <v>6.9748614976461063</v>
+      </c>
+      <c r="J7">
+        <v>35.5488</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="2"/>
+        <v>0.45159999999999911</v>
+      </c>
+      <c r="L7" s="1">
+        <f t="shared" si="3"/>
+        <v>21.050668904115945</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>18</v>
       </c>
@@ -893,8 +1197,30 @@
       <c r="F8">
         <v>33.154800000000002</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>35.495899999999999</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>2.3410999999999973</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="1"/>
+        <v>6.8676515453756002</v>
+      </c>
+      <c r="J8">
+        <v>33.623399999999997</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="2"/>
+        <v>0.46859999999999502</v>
+      </c>
+      <c r="L8" s="1">
+        <f t="shared" si="3"/>
+        <v>20.016231685959401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>212</v>
       </c>
@@ -907,8 +1233,30 @@
       <c r="F9">
         <v>31.262699999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G9">
+        <v>33.7819</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>2.5192000000000014</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="1"/>
+        <v>6.7533623391210913</v>
+      </c>
+      <c r="J9">
+        <v>31.758700000000001</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="2"/>
+        <v>0.49600000000000222</v>
+      </c>
+      <c r="L9" s="1">
+        <f t="shared" si="3"/>
+        <v>19.688790092092802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>19</v>
       </c>
@@ -920,6 +1268,28 @@
       </c>
       <c r="F10">
         <v>34.545499999999997</v>
+      </c>
+      <c r="G10">
+        <v>37.042099999999998</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>2.4966000000000008</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="1"/>
+        <v>6.6624858229368229</v>
+      </c>
+      <c r="J10">
+        <v>35.045499999999997</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="1">
+        <f t="shared" si="3"/>
+        <v>20.027237042377628</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFAFAC6-669B-4915-9A35-48C26E68B2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E6066D-4C21-42C7-AE33-CA3A6A01CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
   <si>
     <t>Description</t>
   </si>
@@ -213,6 +213,9 @@
   </si>
   <si>
     <t>%ash</t>
+  </si>
+  <si>
+    <t>std</t>
   </si>
 </sst>
 </file>
@@ -567,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="56.33203125" bestFit="1" customWidth="1"/>
@@ -670,6 +673,23 @@
       </c>
       <c r="I4">
         <v>7.04</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E6066D-4C21-42C7-AE33-CA3A6A01CA6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091B6FE7-6EEE-4B5D-9F5A-A43EB8007429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
@@ -182,9 +182,6 @@
     <t>m(sample, wet) [g]</t>
   </si>
   <si>
-    <t>m(container) [g]</t>
-  </si>
-  <si>
     <t>Untr</t>
   </si>
   <si>
@@ -216,6 +213,9 @@
   </si>
   <si>
     <t>std</t>
+  </si>
+  <si>
+    <t>m(crucible) [g]</t>
   </si>
 </sst>
 </file>
@@ -677,7 +677,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -724,10 +724,10 @@
         <v>27</v>
       </c>
       <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
         <v>33</v>
-      </c>
-      <c r="G1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -955,7 +955,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1" t="s">
         <v>28</v>
@@ -967,25 +967,25 @@
         <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
         <v>35</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>36</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>37</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>38</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>39</v>
-      </c>
-      <c r="L1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -993,7 +993,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3">
         <v>30.201000000000001</v>
@@ -1029,7 +1029,7 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>31.4588</v>
@@ -1065,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>31.767600000000002</v>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091B6FE7-6EEE-4B5D-9F5A-A43EB8007429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0E3AB6-B288-4E28-96C5-68B8175BEA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
   <si>
     <t>Description</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>m(crucible) [g]</t>
+  </si>
+  <si>
+    <t>expected weight</t>
   </si>
 </sst>
 </file>
@@ -699,18 +702,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F7390D-8C65-402E-B031-C0A94901E7D3}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -721,16 +724,19 @@
         <v>24</v>
       </c>
       <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -741,17 +747,20 @@
         <v>1.0589</v>
       </c>
       <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>41</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>50</v>
       </c>
-      <c r="G2" s="1">
-        <f>((E2*F2)/D2)/1000</f>
+      <c r="H2" s="1">
+        <f>((F2*G2*E2)/D2)/1000</f>
         <v>1.9359712909623195</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -762,17 +771,20 @@
         <v>1.0946</v>
       </c>
       <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
         <v>44</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>50</v>
       </c>
-      <c r="G3" s="1">
-        <f t="shared" ref="G3:G12" si="0">((E3*F3)/D3)/1000</f>
+      <c r="H3" s="1">
+        <f t="shared" ref="H3:H12" si="0">((F3*G3*E3)/D3)/1000</f>
         <v>2.0098666179426274</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>15</v>
       </c>
@@ -780,17 +792,20 @@
         <v>1.0609999999999999</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>41</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>50</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <f t="shared" si="0"/>
         <v>1.9321394910461829</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>16</v>
       </c>
@@ -798,17 +813,20 @@
         <v>1.0511999999999999</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>39</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>50</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <f t="shared" si="0"/>
         <v>1.8550228310502284</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>17</v>
       </c>
@@ -816,17 +834,20 @@
         <v>1.0470999999999999</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>38</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>50</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <f t="shared" si="0"/>
         <v>1.8145353834399773</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>18</v>
       </c>
@@ -834,17 +855,20 @@
         <v>1.0250999999999999</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>39</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>50</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <f t="shared" si="0"/>
         <v>1.9022534386889085</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>19</v>
       </c>
@@ -852,17 +876,20 @@
         <v>1.0347999999999999</v>
       </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>39</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>50</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>1.8844221105527641</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>20</v>
       </c>
@@ -870,17 +897,20 @@
         <v>1.0647</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <v>36</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>50</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>1.6906170752324599</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>21</v>
       </c>
@@ -888,17 +918,20 @@
         <v>1.0263</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>39</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>50</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>1.900029231218942</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>22</v>
       </c>
@@ -906,17 +939,20 @@
         <v>0.49199999999999999</v>
       </c>
       <c r="E11">
+        <v>0.5</v>
+      </c>
+      <c r="F11">
         <v>67</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>50</v>
       </c>
-      <c r="G11" s="1">
-        <f t="shared" si="0"/>
-        <v>6.808943089430894</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>3.404471544715447</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>23</v>
       </c>
@@ -924,14 +960,17 @@
         <v>0.49830000000000002</v>
       </c>
       <c r="E12">
+        <v>0.5</v>
+      </c>
+      <c r="F12">
         <v>57</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>50</v>
       </c>
-      <c r="G12" s="1">
-        <f t="shared" si="0"/>
-        <v>5.7194461167971102</v>
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>2.8597230583985551</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0E3AB6-B288-4E28-96C5-68B8175BEA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA27460-30B8-46C7-BFA0-431041828D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA27460-30B8-46C7-BFA0-431041828D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1027DC6-B297-4E18-87D7-8EBD75E6ABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
   <si>
     <t>Description</t>
   </si>
@@ -218,16 +218,23 @@
     <t>m(crucible) [g]</t>
   </si>
   <si>
-    <t>expected weight</t>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>stdev</t>
+  </si>
+  <si>
+    <t>expected weight [g]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -271,11 +278,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,7 +710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F7390D-8C65-402E-B031-C0A94901E7D3}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" bestFit="1" customWidth="1"/>
@@ -713,7 +721,7 @@
     <col min="7" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -724,7 +732,7 @@
         <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -735,8 +743,14 @@
       <c r="H1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -760,7 +774,7 @@
         <v>1.9359712909623195</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -784,7 +798,7 @@
         <v>2.0098666179426274</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>15</v>
       </c>
@@ -801,11 +815,19 @@
         <v>50</v>
       </c>
       <c r="H4" s="1">
-        <f t="shared" si="0"/>
+        <f>((F4*G4*E4)/D4)/1000</f>
         <v>1.9321394910461829</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="1">
+        <f>AVERAGE(H2:H4)</f>
+        <v>1.9593257999837099</v>
+      </c>
+      <c r="J4" s="4">
+        <f>_xlfn.STDEV.P(H2:H4)</f>
+        <v>3.5771975834132649E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>16</v>
       </c>
@@ -826,7 +848,7 @@
         <v>1.8550228310502284</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>17</v>
       </c>
@@ -847,7 +869,7 @@
         <v>1.8145353834399773</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>18</v>
       </c>
@@ -867,8 +889,16 @@
         <f t="shared" si="0"/>
         <v>1.9022534386889085</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="1">
+        <f>AVERAGE(H5:H7)</f>
+        <v>1.8572705510597045</v>
+      </c>
+      <c r="J7" s="4">
+        <f>_xlfn.STDEV.P(H5:H7)</f>
+        <v>3.5845999201160376E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>19</v>
       </c>
@@ -889,7 +919,7 @@
         <v>1.8844221105527641</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>20</v>
       </c>
@@ -910,7 +940,7 @@
         <v>1.6906170752324599</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
         <v>21</v>
       </c>
@@ -930,8 +960,16 @@
         <f t="shared" si="0"/>
         <v>1.900029231218942</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10" s="1">
+        <f>AVERAGE(H8:H10)</f>
+        <v>1.8250228056680553</v>
+      </c>
+      <c r="J10" s="4">
+        <f>_xlfn.STDEV.P(H8:H10)</f>
+        <v>9.5252544443063289E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>22</v>
       </c>
@@ -952,7 +990,7 @@
         <v>3.404471544715447</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>23</v>
       </c>
@@ -969,8 +1007,15 @@
         <v>50</v>
       </c>
       <c r="H12" s="1">
-        <f t="shared" si="0"/>
+        <f>((F12*G12*E12)/D12)/1000</f>
         <v>2.8597230583985551</v>
+      </c>
+      <c r="I12" s="1">
+        <f>AVERAGE(H11:H12)</f>
+        <v>3.1320973015570011</v>
+      </c>
+      <c r="J12" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1027DC6-B297-4E18-87D7-8EBD75E6ABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B441A5EE-E6C5-4C82-9A0E-6E7D6BDCE8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
   <si>
     <t>Description</t>
   </si>
@@ -225,6 +225,9 @@
   </si>
   <si>
     <t>expected weight [g]</t>
+  </si>
+  <si>
+    <t>nan</t>
   </si>
 </sst>
 </file>
@@ -794,7 +797,7 @@
         <v>50</v>
       </c>
       <c r="H3" s="1">
-        <f t="shared" ref="H3:H12" si="0">((F3*G3*E3)/D3)/1000</f>
+        <f t="shared" ref="H3:H11" si="0">((F3*G3*E3)/D3)/1000</f>
         <v>2.0098666179426274</v>
       </c>
     </row>
@@ -1015,7 +1018,7 @@
         <v>3.1320973015570011</v>
       </c>
       <c r="J12" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B441A5EE-E6C5-4C82-9A0E-6E7D6BDCE8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEBD7B6-E3FC-4676-A770-AC9A584C81CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH" sheetId="1" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t>Description</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t>nan</t>
+  </si>
+  <si>
+    <t>% DM mean</t>
+  </si>
+  <si>
+    <t>% DM std-dev</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2D6C95A-479E-4C84-94F4-777190CE73FB}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -1038,9 +1044,10 @@
     <col min="6" max="6" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -1066,16 +1073,22 @@
         <v>36</v>
       </c>
       <c r="J1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" t="s">
         <v>37</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>38</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C2">
         <v>8</v>
       </c>
@@ -1099,19 +1112,19 @@
         <f>(H2/E2)*100</f>
         <v>6.7239495380947627</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <v>32.394799999999996</v>
       </c>
-      <c r="K2">
-        <f>J2-F2</f>
+      <c r="M2">
+        <f>L2-F2</f>
         <v>0.39829999999999544</v>
       </c>
-      <c r="L2" s="1">
-        <f>(K2/H2)*100</f>
+      <c r="N2" s="1">
+        <f>(M2/H2)*100</f>
         <v>19.613926232333458</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C3">
         <v>9</v>
       </c>
@@ -1135,19 +1148,19 @@
         <f t="shared" ref="I3:I10" si="1">(H3/E3)*100</f>
         <v>4.9658601090950842</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <v>34.417700000000004</v>
       </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K10" si="2">J3-F3</f>
+      <c r="M3">
+        <f>L3-F3</f>
         <v>0.41520000000000579</v>
       </c>
-      <c r="L3" s="1">
-        <f t="shared" ref="L3:L10" si="3">(K3/H3)*100</f>
+      <c r="N3" s="1">
+        <f>(M3/H3)*100</f>
         <v>26.57790295736811</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C4">
         <v>5</v>
       </c>
@@ -1172,18 +1185,26 @@
         <v>8.9115954620430742</v>
       </c>
       <c r="J4" s="1">
+        <f>AVERAGE(I2:I4)</f>
+        <v>6.867135036410974</v>
+      </c>
+      <c r="K4" s="1">
+        <f>_xlfn.STDEV.P(I2:I4)</f>
+        <v>1.6140184703759224</v>
+      </c>
+      <c r="L4" s="1">
         <v>33.775100000000002</v>
       </c>
-      <c r="K4" s="3">
-        <f t="shared" si="2"/>
+      <c r="M4" s="3">
+        <f>L4-F4</f>
         <v>0.41799999999999926</v>
       </c>
-      <c r="L4" s="1">
-        <f t="shared" si="3"/>
+      <c r="N4" s="1">
+        <f>(M4/H4)*100</f>
         <v>14.765100671140935</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C5">
         <v>10</v>
       </c>
@@ -1207,19 +1228,19 @@
         <f t="shared" si="1"/>
         <v>7.1155966674834499</v>
       </c>
-      <c r="J5">
+      <c r="L5">
         <v>34.533900000000003</v>
       </c>
-      <c r="K5" s="3">
-        <f t="shared" si="2"/>
+      <c r="M5" s="3">
+        <f>L5-F5</f>
         <v>0.4789999999999992</v>
       </c>
-      <c r="L5" s="1">
-        <f t="shared" si="3"/>
+      <c r="N5" s="1">
+        <f>(M5/H5)*100</f>
         <v>20.619000473505224</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C6">
         <v>20</v>
       </c>
@@ -1243,19 +1264,19 @@
         <f t="shared" si="1"/>
         <v>7.0200063195356739</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>34.061399999999999</v>
       </c>
-      <c r="K6">
-        <f t="shared" si="2"/>
+      <c r="M6">
+        <f>L6-F6</f>
         <v>0.43959999999999866</v>
       </c>
-      <c r="L6" s="1">
-        <f t="shared" si="3"/>
+      <c r="N6" s="1">
+        <f>(M6/H6)*100</f>
         <v>20.828200511702789</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C7">
         <v>15</v>
       </c>
@@ -1279,19 +1300,27 @@
         <f t="shared" si="1"/>
         <v>6.9748614976461063</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
+        <f>AVERAGE(I5:I7)</f>
+        <v>7.03682149488841</v>
+      </c>
+      <c r="K7" s="1">
+        <f>_xlfn.STDEV.P(I5:I7)</f>
+        <v>5.8672308055810758E-2</v>
+      </c>
+      <c r="L7">
         <v>35.5488</v>
       </c>
-      <c r="K7">
-        <f t="shared" si="2"/>
+      <c r="M7">
+        <f>L7-F7</f>
         <v>0.45159999999999911</v>
       </c>
-      <c r="L7" s="1">
-        <f t="shared" si="3"/>
+      <c r="N7" s="1">
+        <f>(M7/H7)*100</f>
         <v>21.050668904115945</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C8">
         <v>18</v>
       </c>
@@ -1315,19 +1344,19 @@
         <f t="shared" si="1"/>
         <v>6.8676515453756002</v>
       </c>
-      <c r="J8">
+      <c r="L8">
         <v>33.623399999999997</v>
       </c>
-      <c r="K8">
-        <f t="shared" si="2"/>
+      <c r="M8">
+        <f>L8-F8</f>
         <v>0.46859999999999502</v>
       </c>
-      <c r="L8" s="1">
-        <f t="shared" si="3"/>
+      <c r="N8" s="1">
+        <f>(M8/H8)*100</f>
         <v>20.016231685959401</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C9">
         <v>212</v>
       </c>
@@ -1351,19 +1380,19 @@
         <f t="shared" si="1"/>
         <v>6.7533623391210913</v>
       </c>
-      <c r="J9">
+      <c r="L9">
         <v>31.758700000000001</v>
       </c>
-      <c r="K9" s="3">
-        <f t="shared" si="2"/>
+      <c r="M9" s="3">
+        <f>L9-F9</f>
         <v>0.49600000000000222</v>
       </c>
-      <c r="L9" s="1">
-        <f t="shared" si="3"/>
+      <c r="N9" s="1">
+        <f>(M9/H9)*100</f>
         <v>19.688790092092802</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C10">
         <v>19</v>
       </c>
@@ -1387,15 +1416,23 @@
         <f t="shared" si="1"/>
         <v>6.6624858229368229</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="1">
+        <f>AVERAGE(I8:I10)</f>
+        <v>6.7611665691445042</v>
+      </c>
+      <c r="K10" s="1">
+        <f>_xlfn.STDEV.P(I8:I10)</f>
+        <v>8.3940148997763531E-2</v>
+      </c>
+      <c r="L10">
         <v>35.045499999999997</v>
       </c>
-      <c r="K10" s="3">
-        <f t="shared" si="2"/>
+      <c r="M10" s="3">
+        <f>L10-F10</f>
         <v>0.5</v>
       </c>
-      <c r="L10" s="1">
-        <f t="shared" si="3"/>
+      <c r="N10" s="1">
+        <f>(M10/H10)*100</f>
         <v>20.027237042377628</v>
       </c>
     </row>

--- a/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
+++ b/Lab-trails/2026-01-06-cattle-slurry/2026-01-06-cattle-slurry-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-01-06-cattle-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEBD7B6-E3FC-4676-A770-AC9A584C81CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B09E01-7934-4D9F-8346-C7952301E8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -218,9 +218,6 @@
     <t>m(crucible) [g]</t>
   </si>
   <si>
-    <t>mean</t>
-  </si>
-  <si>
     <t>stdev</t>
   </si>
   <si>
@@ -234,6 +231,9 @@
   </si>
   <si>
     <t>% DM std-dev</t>
+  </si>
+  <si>
+    <t>mean [g/L]</t>
   </si>
 </sst>
 </file>
@@ -741,7 +741,7 @@
         <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F1" t="s">
         <v>27</v>
@@ -753,10 +753,10 @@
         <v>33</v>
       </c>
       <c r="I1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" t="s">
         <v>42</v>
-      </c>
-      <c r="J1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -1024,7 +1024,7 @@
         <v>3.1320973015570011</v>
       </c>
       <c r="J12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1073,10 +1073,10 @@
         <v>36</v>
       </c>
       <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
         <v>46</v>
-      </c>
-      <c r="K1" t="s">
-        <v>47</v>
       </c>
       <c r="L1" t="s">
         <v>37</v>
@@ -1116,11 +1116,11 @@
         <v>32.394799999999996</v>
       </c>
       <c r="M2">
-        <f>L2-F2</f>
+        <f t="shared" ref="M2:M10" si="0">L2-F2</f>
         <v>0.39829999999999544</v>
       </c>
       <c r="N2" s="1">
-        <f>(M2/H2)*100</f>
+        <f t="shared" ref="N2:N10" si="1">(M2/H2)*100</f>
         <v>19.613926232333458</v>
       </c>
     </row>
@@ -1141,22 +1141,22 @@
         <v>35.564700000000002</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H10" si="0">G3-F3</f>
+        <f t="shared" ref="H3:H10" si="2">G3-F3</f>
         <v>1.5622000000000043</v>
       </c>
       <c r="I3" s="1">
-        <f t="shared" ref="I3:I10" si="1">(H3/E3)*100</f>
+        <f t="shared" ref="I3:I10" si="3">(H3/E3)*100</f>
         <v>4.9658601090950842</v>
       </c>
       <c r="L3">
         <v>34.417700000000004</v>
       </c>
       <c r="M3">
-        <f>L3-F3</f>
+        <f t="shared" si="0"/>
         <v>0.41520000000000579</v>
       </c>
       <c r="N3" s="1">
-        <f>(M3/H3)*100</f>
+        <f t="shared" si="1"/>
         <v>26.57790295736811</v>
       </c>
     </row>
@@ -1177,11 +1177,11 @@
         <v>36.188099999999999</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.830999999999996</v>
       </c>
       <c r="I4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8.9115954620430742</v>
       </c>
       <c r="J4" s="1">
@@ -1196,11 +1196,11 @@
         <v>33.775100000000002</v>
       </c>
       <c r="M4" s="3">
-        <f>L4-F4</f>
+        <f t="shared" si="0"/>
         <v>0.41799999999999926</v>
       </c>
       <c r="N4" s="1">
-        <f>(M4/H4)*100</f>
+        <f t="shared" si="1"/>
         <v>14.765100671140935</v>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
         <v>36.378</v>
       </c>
       <c r="H5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.3230999999999966</v>
       </c>
       <c r="I5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7.1155966674834499</v>
       </c>
       <c r="L5">
         <v>34.533900000000003</v>
       </c>
       <c r="M5" s="3">
-        <f>L5-F5</f>
+        <f t="shared" si="0"/>
         <v>0.4789999999999992</v>
       </c>
       <c r="N5" s="1">
-        <f>(M5/H5)*100</f>
+        <f t="shared" si="1"/>
         <v>20.619000473505224</v>
       </c>
     </row>
@@ -1257,22 +1257,22 @@
         <v>35.732399999999998</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.110599999999998</v>
       </c>
       <c r="I6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7.0200063195356739</v>
       </c>
       <c r="L6">
         <v>34.061399999999999</v>
       </c>
       <c r="M6">
-        <f>L6-F6</f>
+        <f t="shared" si="0"/>
         <v>0.43959999999999866</v>
       </c>
       <c r="N6" s="1">
-        <f>(M6/H6)*100</f>
+        <f t="shared" si="1"/>
         <v>20.828200511702789</v>
       </c>
     </row>
@@ -1293,11 +1293,11 @@
         <v>37.2425</v>
       </c>
       <c r="H7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.1452999999999989</v>
       </c>
       <c r="I7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.9748614976461063</v>
       </c>
       <c r="J7" s="1">
@@ -1312,11 +1312,11 @@
         <v>35.5488</v>
       </c>
       <c r="M7">
-        <f>L7-F7</f>
+        <f t="shared" si="0"/>
         <v>0.45159999999999911</v>
       </c>
       <c r="N7" s="1">
-        <f>(M7/H7)*100</f>
+        <f t="shared" si="1"/>
         <v>21.050668904115945</v>
       </c>
     </row>
@@ -1337,22 +1337,22 @@
         <v>35.495899999999999</v>
       </c>
       <c r="H8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.3410999999999973</v>
       </c>
       <c r="I8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.8676515453756002</v>
       </c>
       <c r="L8">
         <v>33.623399999999997</v>
       </c>
       <c r="M8">
-        <f>L8-F8</f>
+        <f t="shared" si="0"/>
         <v>0.46859999999999502</v>
       </c>
       <c r="N8" s="1">
-        <f>(M8/H8)*100</f>
+        <f t="shared" si="1"/>
         <v>20.016231685959401</v>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
         <v>33.7819</v>
       </c>
       <c r="H9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.5192000000000014</v>
       </c>
       <c r="I9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.7533623391210913</v>
       </c>
       <c r="L9">
         <v>31.758700000000001</v>
       </c>
       <c r="M9" s="3">
-        <f>L9-F9</f>
+        <f t="shared" si="0"/>
         <v>0.49600000000000222</v>
       </c>
       <c r="N9" s="1">
-        <f>(M9/H9)*100</f>
+        <f t="shared" si="1"/>
         <v>19.688790092092802</v>
       </c>
     </row>
@@ -1409,11 +1409,11 @@
         <v>37.042099999999998</v>
       </c>
       <c r="H10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.4966000000000008</v>
       </c>
       <c r="I10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.6624858229368229</v>
       </c>
       <c r="J10" s="1">
@@ -1428,11 +1428,11 @@
         <v>35.045499999999997</v>
       </c>
       <c r="M10" s="3">
-        <f>L10-F10</f>
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
       <c r="N10" s="1">
-        <f>(M10/H10)*100</f>
+        <f t="shared" si="1"/>
         <v>20.027237042377628</v>
       </c>
     </row>
